--- a/portfolio_sample.xlsx
+++ b/portfolio_sample.xlsx
@@ -413,89 +413,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ticker</t>
+          <t>종목명</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>매입단가</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>AvgPrice</t>
+          <t>보유수량</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>티커</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>70000</v>
       </c>
       <c r="C2" t="n">
-        <v>150</v>
+        <v>100</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="C3" t="n">
-        <v>300</v>
+        <v>10</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>Tencent</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="C4" t="n">
-        <v>180</v>
+        <v>50</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="C5" t="n">
-        <v>120</v>
+        <v>20</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>150000</v>
       </c>
       <c r="C6" t="n">
-        <v>450</v>
+        <v>30</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
       </c>
     </row>
   </sheetData>
